--- a/backend/src/utils/data.xlsx
+++ b/backend/src/utils/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\ThesisBoard\backend\src\utils\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\.workspace\ITITIU21318_TranThien\backend\src\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F11B562-C341-4136-A7AA-FD9F9CBD9282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9964D6-F304-48B3-BA05-D4F88414C86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1935" yWindow="990" windowWidth="21510" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="admin" sheetId="1" r:id="rId1"/>
@@ -1582,6 +1582,7 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="25.5703125" customWidth="1"/>
     <col min="4" max="4" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
